--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2024_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2024_o_higgins.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>4.074498137096816</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>3.604101295774464</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>6.749183288645089</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>2.024295620787875</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>2.049252817899383</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>5.060878570632599</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>0.8878447460197503</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>4.548171466115192</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>3.913688000537974</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>7.160106290587964</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>2.98789166468667</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>3.380264588048942</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>0.3209343612048832</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>4.228559278982158</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -713,9 +666,6 @@
       <c r="E16">
         <v>1.546891264018679</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -735,9 +685,6 @@
       <c r="E17">
         <v>3.4801887372931</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -757,9 +704,6 @@
       <c r="E18">
         <v>1.830017061036049</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -779,9 +723,6 @@
       <c r="E19">
         <v>5.539803033793178</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,9 +742,6 @@
       <c r="E20">
         <v>5.286921261079769</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,9 +761,6 @@
       <c r="E21">
         <v>2.823520175862781</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -845,9 +780,6 @@
       <c r="E22">
         <v>5.102086035249642</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -867,9 +799,6 @@
       <c r="E23">
         <v>5.054992304628469</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -889,9 +818,6 @@
       <c r="E24">
         <v>5.079269479955406</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -911,9 +837,6 @@
       <c r="E25">
         <v>4.52122120191667</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -933,9 +856,6 @@
       <c r="E26">
         <v>5.647449338536048</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -955,9 +875,6 @@
       <c r="E27">
         <v>2.148690866852276</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -977,9 +894,6 @@
       <c r="E28">
         <v>2.5351935036106</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -999,9 +913,6 @@
       <c r="E29">
         <v>6.085935340397031</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1021,9 +932,6 @@
       <c r="E30">
         <v>8.281138630646613</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1043,9 +951,6 @@
       <c r="E31">
         <v>5.232939691946181</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1065,9 +970,6 @@
       <c r="E32">
         <v>6.854583060501174</v>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1087,9 +989,6 @@
       <c r="E33">
         <v>-2.110304398739016</v>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1108,9 +1007,6 @@
       </c>
       <c r="E34">
         <v>14.13673561023758</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2024_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2024_o_higgins.xlsx
@@ -480,191 +480,191 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B7">
-        <v>385884.31</v>
+        <v>391630.25</v>
       </c>
       <c r="C7">
-        <v>367295.91</v>
+        <v>376555.31</v>
       </c>
       <c r="D7">
-        <v>18588.40000000002</v>
+        <v>15074.94</v>
       </c>
       <c r="E7">
-        <v>5.060878570632599</v>
+        <v>4.003380008105584</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Codegua</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="B8">
-        <v>385554.41</v>
+        <v>385884.31</v>
       </c>
       <c r="C8">
-        <v>382161.41</v>
+        <v>367295.91</v>
       </c>
       <c r="D8">
-        <v>3393</v>
+        <v>18588.40000000002</v>
       </c>
       <c r="E8">
-        <v>0.8878447460197503</v>
+        <v>5.060878570632599</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Doñihue</t>
+          <t>Codegua</t>
         </is>
       </c>
       <c r="B9">
-        <v>384034.31</v>
+        <v>385554.41</v>
       </c>
       <c r="C9">
-        <v>367327.62</v>
+        <v>382161.41</v>
       </c>
       <c r="D9">
-        <v>16706.69</v>
+        <v>3393</v>
       </c>
       <c r="E9">
-        <v>4.548171466115192</v>
+        <v>0.8878447460197503</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Doñihue</t>
         </is>
       </c>
       <c r="B10">
-        <v>361903.09</v>
+        <v>384034.31</v>
       </c>
       <c r="C10">
-        <v>348272.78</v>
+        <v>367327.62</v>
       </c>
       <c r="D10">
-        <v>13630.31</v>
+        <v>16706.69</v>
       </c>
       <c r="E10">
-        <v>3.913688000537974</v>
+        <v>4.548171466115192</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="B11">
-        <v>358815.5</v>
+        <v>361903.09</v>
       </c>
       <c r="C11">
-        <v>334840.56</v>
+        <v>348272.78</v>
       </c>
       <c r="D11">
-        <v>23974.94</v>
+        <v>13630.31</v>
       </c>
       <c r="E11">
-        <v>7.160106290587964</v>
+        <v>3.913688000537974</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Coltauco</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="B12">
-        <v>333673.91</v>
+        <v>358815.5</v>
       </c>
       <c r="C12">
-        <v>323993.34</v>
+        <v>334840.56</v>
       </c>
       <c r="D12">
-        <v>9680.569999999949</v>
+        <v>23974.94</v>
       </c>
       <c r="E12">
-        <v>2.98789166468667</v>
+        <v>7.160106290587964</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Coltauco</t>
         </is>
       </c>
       <c r="B13">
-        <v>332554.09</v>
+        <v>333673.91</v>
       </c>
       <c r="C13">
-        <v>321680.44</v>
+        <v>323993.34</v>
       </c>
       <c r="D13">
-        <v>10873.65000000002</v>
+        <v>9680.569999999949</v>
       </c>
       <c r="E13">
-        <v>3.380264588048942</v>
+        <v>2.98789166468667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Coinco</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="B14">
-        <v>322868.16</v>
+        <v>332554.09</v>
       </c>
       <c r="C14">
-        <v>321835.28</v>
+        <v>321680.44</v>
       </c>
       <c r="D14">
-        <v>1032.879999999946</v>
+        <v>10873.65000000002</v>
       </c>
       <c r="E14">
-        <v>0.3209343612048832</v>
+        <v>3.380264588048942</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Coinco</t>
         </is>
       </c>
       <c r="B15">
-        <v>321091.19</v>
+        <v>322868.16</v>
       </c>
       <c r="C15">
-        <v>308064.5</v>
+        <v>321835.28</v>
       </c>
       <c r="D15">
-        <v>13026.69</v>
+        <v>1032.879999999946</v>
       </c>
       <c r="E15">
-        <v>4.228559278982158</v>
+        <v>0.3209343612048832</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marchihue</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="B16">
-        <v>320562.81</v>
+        <v>321091.19</v>
       </c>
       <c r="C16">
-        <v>315679.59</v>
+        <v>308064.5</v>
       </c>
       <c r="D16">
-        <v>4883.219999999972</v>
+        <v>13026.69</v>
       </c>
       <c r="E16">
-        <v>1.546891264018679</v>
+        <v>4.228559278982158</v>
       </c>
     </row>
     <row r="17">
@@ -1016,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1164,200 +1164,190 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marchihue</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="B15">
-        <v>320562.81</v>
+        <v>361903.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="B16">
-        <v>361903.09</v>
+        <v>299385.34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="B17">
-        <v>299385.34</v>
+        <v>247564.38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="B18">
-        <v>247564.38</v>
+        <v>433084.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Palmilla</t>
         </is>
       </c>
       <c r="B19">
-        <v>433084.97</v>
+        <v>281826.84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Palmilla</t>
+          <t>Paredones</t>
         </is>
       </c>
       <c r="B20">
-        <v>281826.84</v>
+        <v>186221.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="B21">
-        <v>186221.64</v>
+        <v>308563.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="B22">
-        <v>308563.22</v>
+        <v>332554.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="B23">
-        <v>332554.09</v>
+        <v>288503.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="B24">
-        <v>288503.94</v>
+        <v>262426.38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="B25">
-        <v>262426.38</v>
+        <v>293911.84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="B26">
-        <v>293911.84</v>
+        <v>244116.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="B27">
-        <v>244116.89</v>
+        <v>290214.91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="B28">
-        <v>290214.91</v>
+        <v>478451.22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="B29">
-        <v>478451.22</v>
+        <v>358815.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="B30">
-        <v>358815.5</v>
+        <v>431807.69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="B31">
-        <v>431807.69</v>
+        <v>385884.31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="B32">
-        <v>385884.31</v>
+        <v>319535.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="B33">
-        <v>319535.44</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="B34">
         <v>321091.19</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2024_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2024_o_higgins.xlsx
@@ -1016,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1025,330 +1025,236 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chépica</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>241598.8</v>
+          <t>Marchigüe</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>292197</v>
+          <t>Codegua</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codegua</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>385554.41</v>
+          <t>Coinco</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coinco</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>322868.16</v>
+          <t>Coltauco</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coltauco</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>333673.91</v>
+          <t>Graneros</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Doñihue</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>384034.31</v>
+          <t>Malloa</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Graneros</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>394752.41</v>
+          <t>Peumo</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>La Estrella</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>264112.56</v>
+          <t>Pichidegua</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>308074.78</v>
+          <t>Rancagua</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Litueche</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>256398.45</v>
+          <t>Requínoa</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lolol</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>206780.94</v>
+          <t>Mostazal</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machalí</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>752037.38</v>
+          <t>San Vicente</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Malloa</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>274461.16</v>
+          <t>Nancagua</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mostazal</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>361903.09</v>
+          <t>Peralillo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nancagua</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>299385.34</v>
+          <t>Placilla</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Navidad</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>247564.38</v>
+          <t>Pumanque</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Olivar</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>433084.97</v>
+          <t>Paredones</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Palmilla</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>281826.84</v>
+          <t>Pichilemu</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paredones</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>186221.64</v>
+          <t>Litueche</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Peralillo</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>308563.22</v>
+          <t>Navidad</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peumo</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>332554.09</v>
+          <t>La Estrella</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>288503.94</v>
+          <t>Doñihue</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>262426.38</v>
+          <t>Olivar</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Placilla</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>293911.84</v>
+          <t>Rengo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pumanque</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>244116.89</v>
+          <t>Santa Cruz</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>290214.91</v>
+          <t>Palmilla</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rancagua</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>478451.22</v>
+          <t>Quinta de Tilcoco</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rengo</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>358815.5</v>
+          <t>Machalí</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Requínoa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>431807.69</v>
+          <t>Las Cabras</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Fernando</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>385884.31</v>
+          <t>Chimbarongo</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>319535.44</v>
+          <t>Lolol</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>321091.19</v>
+          <t>Chépica</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
       </c>
     </row>
   </sheetData>
